--- a/data_raw/city_income.xlsx
+++ b/data_raw/city_income.xlsx
@@ -1,216 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>地方一般公共预算收入(亿元)</t>
-  </si>
-  <si>
-    <t>上海</t>
-  </si>
-  <si>
-    <t>乌鲁木齐</t>
-  </si>
-  <si>
-    <t>兰州</t>
-  </si>
-  <si>
-    <t>北京</t>
-  </si>
-  <si>
-    <t>南京</t>
-  </si>
-  <si>
-    <t>南宁</t>
-  </si>
-  <si>
-    <t>南昌</t>
-  </si>
-  <si>
-    <t>厦门</t>
-  </si>
-  <si>
-    <t>合肥</t>
-  </si>
-  <si>
-    <t>呼和浩特</t>
-  </si>
-  <si>
-    <t>哈尔滨</t>
-  </si>
-  <si>
-    <t>大连</t>
-  </si>
-  <si>
-    <t>天津</t>
-  </si>
-  <si>
-    <t>太原</t>
-  </si>
-  <si>
-    <t>宁波</t>
-  </si>
-  <si>
-    <t>广州</t>
-  </si>
-  <si>
-    <t>成都</t>
-  </si>
-  <si>
-    <t>拉萨</t>
-  </si>
-  <si>
-    <t>昆明</t>
-  </si>
-  <si>
-    <t>杭州</t>
-  </si>
-  <si>
-    <t>武汉</t>
-  </si>
-  <si>
-    <t>沈阳</t>
-  </si>
-  <si>
-    <t>济南</t>
-  </si>
-  <si>
-    <t>海口</t>
-  </si>
-  <si>
-    <t>深圳</t>
-  </si>
-  <si>
-    <t>石家庄</t>
-  </si>
-  <si>
-    <t>福州</t>
-  </si>
-  <si>
-    <t>西宁</t>
-  </si>
-  <si>
-    <t>西安</t>
-  </si>
-  <si>
-    <t>贵阳</t>
-  </si>
-  <si>
-    <t>郑州</t>
-  </si>
-  <si>
-    <t>重庆</t>
-  </si>
-  <si>
-    <t>银川</t>
-  </si>
-  <si>
-    <t>长春</t>
-  </si>
-  <si>
-    <t>长沙</t>
-  </si>
-  <si>
-    <t>青岛</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -225,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -541,2302 +420,2458 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>地方一般公共预算收入(亿元)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>1576.0742</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>2074.4792</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>2358.7464</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>2540.2975</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>2873.584</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>3429.83</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>3743.7053</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>4109.5086</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>4585.5534</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>5519.5</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>6406.13</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>6642.2638</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>7108.148</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>7165.0984</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>7046.2987</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>7771.8002</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>7608</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>8312.5</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>8374.166499999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3">
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>乌鲁木齐</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>57.0356</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>73.42789999999999</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>100.98</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>113.538</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>147.9938</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>229.5887</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>252.0052</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>301.9047</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>340.6243</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>368.6663</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>369.6734</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>400.7781</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>458.2753</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>472.4647</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>392.6378</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>377.926</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>314.8203</v>
       </c>
-      <c r="S3">
+      <c r="S3" t="n">
         <v>369.7888</v>
       </c>
-      <c r="T3">
+      <c r="T3" t="n">
         <v>371.3048</v>
       </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4">
+      <c r="U3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>33.1417</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>46.6256</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>50.8618</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>57.0385</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>72.75790000000001</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>86.4897</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>103.7303</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>124.4956</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>152.3299</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>185.1917</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>215.4794</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>234.2001</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>253.3169</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>233.2261</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>247.131</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>276.7279</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>220.9765</v>
       </c>
-      <c r="S4">
+      <c r="S4" t="n">
         <v>255.3279</v>
       </c>
-      <c r="T4">
+      <c r="T4" t="n">
         <v>251.9062</v>
       </c>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5">
+      <c r="U4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>1117.1514</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>1492.638</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>1837.3238</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>2026.8089</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>2353.9301</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>3006.28</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>3314.934</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>3661.1097</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>4027.1609</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>4723.86</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>5081.26</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>5430.7875</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>5785.9176</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>5817.0994</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>5483.8866</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>5932.308</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>5714.3583</v>
       </c>
-      <c r="S5">
+      <c r="S5" t="n">
         <v>6181.1</v>
       </c>
-      <c r="T5">
+      <c r="T5" t="n">
         <v>6372.6778</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6">
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>246.4392</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>330.1883</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>386.56</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>434.508</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>518.8008</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>635.0018</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>733.0168</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>831.3076</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>903.489</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>1020.03</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>1142.6</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>1271.9111</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>1470.0152</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>1580.03</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>1637.7</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>1729.518</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>1558.2064</v>
       </c>
-      <c r="S6">
+      <c r="S6" t="n">
         <v>1619.9827</v>
       </c>
-      <c r="T6">
+      <c r="T6" t="n">
         <v>1596.0247</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7">
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>南宁</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>56.6221</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>70.151</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>191.1682</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>120.4628</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>156.0958</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>186.2924</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>229.7183</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>256.2469</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>274.8517</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>297.0501</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>312.7921</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>332.15</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>358.956</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>370.9283</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>372.2519</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>392</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>392.6795</v>
       </c>
-      <c r="S7">
+      <c r="S7" t="n">
         <v>400.8778</v>
       </c>
-      <c r="T7">
+      <c r="T7" t="n">
         <v>381.1575</v>
       </c>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>68.1075</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>87.2199</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>102.1477</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>115.8798</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>146.465</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>187.0259</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>240.0205</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>291.9097</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>342.2065</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>389.3412</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>402.1831</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>417.0774</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>461.7462</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>476.9998</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>483.8581</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>484.8319</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>457.678</v>
       </c>
-      <c r="S8">
+      <c r="S8" t="n">
         <v>500.1818</v>
       </c>
-      <c r="T8">
+      <c r="T8" t="n">
         <v>526.2059</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>厦门</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>136.1653</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>186.5262</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>220.2343</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>240.5608</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>289.1748</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>370.7718</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>422.9089</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>490.5996</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>543.7986</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>606.0967000000001</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>647.9366</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>696.866</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>754.5412</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>768.3751</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>783.9392</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>880.9611</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>883.8107</v>
       </c>
-      <c r="S9">
+      <c r="S9" t="n">
         <v>932.1359</v>
       </c>
-      <c r="T9">
+      <c r="T9" t="n">
         <v>933.3486</v>
       </c>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10">
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>79.4046</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>169.3175</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>222.0776</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>180.8977</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>259.4283</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>338.5113</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>389.4991</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>438.6226</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>500.342</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>571.544</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>614.8493</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>655.9039</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>712.4862000000001</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>745.9934</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>762.9009</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>844.2188</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>909.2546</v>
       </c>
-      <c r="S10">
+      <c r="S10" t="n">
         <v>929.6276</v>
       </c>
-      <c r="T10">
+      <c r="T10" t="n">
         <v>955.0095</v>
       </c>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11">
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>45.5202</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>57.9618</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>82.24590000000001</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>106.7947</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>126.7617</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>151.4252</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>178.6447</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>182.0177</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>211.5389</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>247.4021</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>269.653</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>201.502</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>204.7198</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>203.1169</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>217.1024</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>228.9248</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>230.8711</v>
       </c>
-      <c r="S11">
+      <c r="S11" t="n">
         <v>238.0592</v>
       </c>
-      <c r="T11">
+      <c r="T11" t="n">
         <v>255.1216</v>
       </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12">
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>118.2934</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>132.0495</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>164.0056</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>193.3598</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>238.1428</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>300.319</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>354.716</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>402.2808</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>423.5203</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>407.7328</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>376.2384</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>368.1048</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>384.3671</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>370.9066</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>339.5674</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>365.8149</v>
       </c>
-      <c r="S12">
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
         <v>313.0744</v>
       </c>
-      <c r="T12">
+      <c r="T12" t="n">
         <v>337.8436</v>
       </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13">
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>大连</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>196.1357</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>267.9757</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>339.0691</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>400.234</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>500.8322</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>651.1266000000001</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>750.1085</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>850.1646</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>780.8645</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>579.913</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>611.9041</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>657.6367</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>703.9857</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>692.8397</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>702.6822</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>737.5978</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>669.766</v>
       </c>
-      <c r="S13">
+      <c r="S13" t="n">
         <v>750.2361</v>
       </c>
-      <c r="T13">
+      <c r="T13" t="n">
         <v>774.7741</v>
       </c>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14">
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>417.0479</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>540.439</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>675.6186</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>821.9915999999999</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>1068.8093</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>1455.13</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>1760.0201</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>2079.0716</v>
       </c>
-      <c r="J14">
+      <c r="J14" t="n">
         <v>2390.3518</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="n">
         <v>2667.11</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>2723.5</v>
       </c>
-      <c r="M14">
+      <c r="M14" t="n">
         <v>2310.3552</v>
       </c>
-      <c r="N14">
+      <c r="N14" t="n">
         <v>2106.2397</v>
       </c>
-      <c r="O14">
+      <c r="O14" t="n">
         <v>2410.41</v>
       </c>
-      <c r="P14">
+      <c r="P14" t="n">
         <v>1923.1103</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" t="n">
         <v>2141.0606</v>
       </c>
-      <c r="R14">
+      <c r="R14" t="n">
         <v>1846.6866</v>
       </c>
-      <c r="S14">
+      <c r="S14" t="n">
         <v>2027.51</v>
       </c>
-      <c r="T14">
+      <c r="T14" t="n">
         <v>2134.1963</v>
       </c>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15">
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>75.3306</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>88.417</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>116.9224</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>117.5322</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>138.4809</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>174.7179</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="n">
         <v>215.6654</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="n">
         <v>247.3261</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="n">
         <v>258.8527</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>274.2403</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>282.6893</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="n">
         <v>311.8503</v>
       </c>
-      <c r="N15">
+      <c r="N15" t="n">
         <v>373.2275</v>
       </c>
-      <c r="O15">
+      <c r="O15" t="n">
         <v>386.6164</v>
       </c>
-      <c r="P15">
+      <c r="P15" t="n">
         <v>378.4351</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" t="n">
         <v>423.4439</v>
       </c>
-      <c r="R15">
+      <c r="R15" t="n">
         <v>437.4837</v>
       </c>
-      <c r="S15">
+      <c r="S15" t="n">
         <v>449.2358</v>
       </c>
-      <c r="T15">
+      <c r="T15" t="n">
         <v>440.2649</v>
       </c>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16">
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>257.3799</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>329.1218</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>390.3874</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>432.8003</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>530.9278</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>657.5531</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="n">
         <v>725.5003</v>
       </c>
-      <c r="I16">
+      <c r="I16" t="n">
         <v>792.808</v>
       </c>
-      <c r="J16">
+      <c r="J16" t="n">
         <v>860.6109</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="n">
         <v>1006.4065</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>1114.5409</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="n">
         <v>1245.288</v>
       </c>
-      <c r="N16">
+      <c r="N16" t="n">
         <v>1379.6865</v>
       </c>
-      <c r="O16">
+      <c r="O16" t="n">
         <v>1468.5072</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="n">
         <v>1510.8432</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" t="n">
         <v>1723.1388</v>
       </c>
-      <c r="R16">
+      <c r="R16" t="n">
         <v>1680.2309</v>
       </c>
-      <c r="S16">
+      <c r="S16" t="n">
         <v>1785.8565</v>
       </c>
-      <c r="T16">
+      <c r="T16" t="n">
         <v>1790.4654</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>427.0831</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>523.7862</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>621.8355</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>702.6527</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>872.647</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>979.48</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="n">
         <v>1102.3961</v>
       </c>
-      <c r="I17">
+      <c r="I17" t="n">
         <v>1141.8044</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="n">
         <v>1243.1035</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>1349.4742</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>1393.6442</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="n">
         <v>1536.7365</v>
       </c>
-      <c r="N17">
+      <c r="N17" t="n">
         <v>1634.2242</v>
       </c>
-      <c r="O17">
+      <c r="O17" t="n">
         <v>1699.0383</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="n">
         <v>1722.7892</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" t="n">
         <v>1884.257</v>
       </c>
-      <c r="R17">
+      <c r="R17" t="n">
         <v>1855.0953</v>
       </c>
-      <c r="S17">
+      <c r="S17" t="n">
         <v>1945.0562</v>
       </c>
-      <c r="T17">
+      <c r="T17" t="n">
         <v>1954.7351</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18">
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>186.7703</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>286.3772</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>354.6938</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>387.3626</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>526.9400000000001</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>680.6929</v>
       </c>
-      <c r="H18">
+      <c r="H18" t="n">
         <v>780.8952</v>
       </c>
-      <c r="I18">
+      <c r="I18" t="n">
         <v>898.5395</v>
       </c>
-      <c r="J18">
+      <c r="J18" t="n">
         <v>1025.1696</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="n">
         <v>1157.6393</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>1175.4109</v>
       </c>
-      <c r="M18">
+      <c r="M18" t="n">
         <v>1275.5334</v>
       </c>
-      <c r="N18">
+      <c r="N18" t="n">
         <v>1424.155</v>
       </c>
-      <c r="O18">
+      <c r="O18" t="n">
         <v>1482.9607</v>
       </c>
-      <c r="P18">
+      <c r="P18" t="n">
         <v>1520.3788</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" t="n">
         <v>1697.6341</v>
       </c>
-      <c r="R18">
+      <c r="R18" t="n">
         <v>1722.4332</v>
       </c>
-      <c r="S18">
+      <c r="S18" t="n">
         <v>1929.057</v>
       </c>
-      <c r="T18">
+      <c r="T18" t="n">
         <v>1949.4956</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19">
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>拉萨</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>3.8976</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>5.7466</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>8.030799999999999</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>10.0467</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>15.0159</v>
       </c>
-      <c r="G19">
+      <c r="G19" t="n">
         <v>23.4291</v>
       </c>
-      <c r="H19">
+      <c r="H19" t="n">
         <v>34.3567</v>
       </c>
-      <c r="I19">
+      <c r="I19" t="n">
         <v>50.1616</v>
       </c>
-      <c r="J19">
+      <c r="J19" t="n">
         <v>64.7891</v>
       </c>
-      <c r="K19">
+      <c r="K19" t="n">
         <v>62.4162</v>
       </c>
-      <c r="L19">
+      <c r="L19" t="n">
         <v>70.7891</v>
       </c>
-      <c r="M19">
+      <c r="M19" t="n">
         <v>89.6288</v>
       </c>
-      <c r="N19">
+      <c r="N19" t="n">
         <v>110.103</v>
       </c>
-      <c r="O19">
+      <c r="O19" t="n">
         <v>117.0407</v>
       </c>
-      <c r="P19">
+      <c r="P19" t="n">
         <v>107.2584</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" t="n">
         <v>106.9404</v>
       </c>
-      <c r="R19">
+      <c r="R19" t="n">
         <v>72.47490000000001</v>
       </c>
-      <c r="S19">
+      <c r="S19" t="n">
         <v>109.137</v>
       </c>
-      <c r="T19">
+      <c r="T19" t="n">
         <v>120.6387</v>
       </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20">
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>103.716</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>133.0993</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>174.9894</v>
       </c>
-      <c r="F20">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
         <v>253.8316</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>317.6893</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="n">
         <v>378.3951</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>450.7534</v>
       </c>
-      <c r="J20">
+      <c r="J20" t="n">
         <v>477.9736</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="n">
         <v>502.2161</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>530.0026</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="n">
         <v>560.8643</v>
       </c>
-      <c r="N20">
+      <c r="N20" t="n">
         <v>595.6333</v>
       </c>
-      <c r="O20">
+      <c r="O20" t="n">
         <v>630.0303</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="n">
         <v>650.4738</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" t="n">
         <v>689.1172</v>
       </c>
-      <c r="R20">
+      <c r="R20" t="n">
         <v>505.2456</v>
       </c>
-      <c r="S20">
+      <c r="S20" t="n">
         <v>558.0042</v>
       </c>
-      <c r="T20">
+      <c r="T20" t="n">
         <v>547.2211</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21">
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>301.3888</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>391.6195</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>455.3531</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>520.7899</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>671.3413</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>785.1523999999999</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="n">
         <v>859.9875</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>945.202</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="n">
         <v>1027.3169</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="n">
         <v>1233.882</v>
       </c>
-      <c r="L21">
+      <c r="L21" t="n">
         <v>1402.3826</v>
       </c>
-      <c r="M21">
+      <c r="M21" t="n">
         <v>1567.4169</v>
       </c>
-      <c r="N21">
+      <c r="N21" t="n">
         <v>1825.0616</v>
       </c>
-      <c r="O21">
+      <c r="O21" t="n">
         <v>1965.9731</v>
       </c>
-      <c r="P21">
+      <c r="P21" t="n">
         <v>2093.3893</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" t="n">
         <v>2386.5936</v>
       </c>
-      <c r="R21">
+      <c r="R21" t="n">
         <v>2450.6119</v>
       </c>
-      <c r="S21">
+      <c r="S21" t="n">
         <v>2616.8107</v>
       </c>
-      <c r="T21">
+      <c r="T21" t="n">
         <v>2640.3344</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22">
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>178.6021</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>221.6755</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>277.3176</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>316.0716</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>390.1866</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>673.26</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="n">
         <v>828.5846</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>978.52</v>
       </c>
-      <c r="J22">
+      <c r="J22" t="n">
         <v>1101.0207</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="n">
         <v>1245.6338</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>1322.0962</v>
       </c>
-      <c r="M22">
+      <c r="M22" t="n">
         <v>1402.9265</v>
       </c>
-      <c r="N22">
+      <c r="N22" t="n">
         <v>1528.6984</v>
       </c>
-      <c r="O22">
+      <c r="O22" t="n">
         <v>1564.1163</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="n">
         <v>1230.2897</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" t="n">
         <v>1578.6488</v>
       </c>
-      <c r="R22">
+      <c r="R22" t="n">
         <v>1504.7392</v>
       </c>
-      <c r="S22">
+      <c r="S22" t="n">
         <v>1601.199</v>
       </c>
-      <c r="T22">
+      <c r="T22" t="n">
         <v>1667.3101</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23">
+      <c r="U22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>175.6336</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>230.8085</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>291.0381</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>320.207</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>465.354</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>620.1242999999999</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="n">
         <v>715.0377</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>800.9997</v>
       </c>
-      <c r="J23">
+      <c r="J23" t="n">
         <v>785.502</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="n">
         <v>606.2411</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>620.9494</v>
       </c>
-      <c r="M23">
+      <c r="M23" t="n">
         <v>656.2406</v>
       </c>
-      <c r="N23">
+      <c r="N23" t="n">
         <v>720.6425</v>
       </c>
-      <c r="O23">
+      <c r="O23" t="n">
         <v>730.2853</v>
       </c>
-      <c r="P23">
+      <c r="P23" t="n">
         <v>736.0802</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" t="n">
         <v>773.0201</v>
       </c>
-      <c r="R23">
+      <c r="R23" t="n">
         <v>713.6722</v>
       </c>
-      <c r="S23">
+      <c r="S23" t="n">
         <v>800.8539</v>
       </c>
-      <c r="T23">
+      <c r="T23" t="n">
         <v>825.5809</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24">
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>128.4388</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>157.0192</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>186.0155</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>210.1923</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>266.1314</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>325.4165</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="n">
         <v>380.8218</v>
       </c>
-      <c r="I24">
+      <c r="I24" t="n">
         <v>482.0722</v>
       </c>
-      <c r="J24">
+      <c r="J24" t="n">
         <v>543.1278</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="n">
         <v>614.3172</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>641.2166999999999</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="n">
         <v>677.21</v>
       </c>
-      <c r="N24">
+      <c r="N24" t="n">
         <v>752.8162</v>
       </c>
-      <c r="O24">
+      <c r="O24" t="n">
         <v>874.1898</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="n">
         <v>906.0751</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" t="n">
         <v>1007.6073</v>
       </c>
-      <c r="R24">
+      <c r="R24" t="n">
         <v>1001.1421</v>
       </c>
-      <c r="S24">
+      <c r="S24" t="n">
         <v>1060.8223</v>
       </c>
-      <c r="T24">
+      <c r="T24" t="n">
         <v>1083.0473</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25">
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>海口</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>21.1288</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>44.8495</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>31.0313</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>38.4416</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>50.3661</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>60.9319</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="n">
         <v>73.1687</v>
       </c>
-      <c r="I25">
+      <c r="I25" t="n">
         <v>86.7324</v>
       </c>
-      <c r="J25">
+      <c r="J25" t="n">
         <v>100.1174</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="n">
         <v>111.5041</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>115.5064</v>
       </c>
-      <c r="M25">
+      <c r="M25" t="n">
         <v>125.3645</v>
       </c>
-      <c r="N25">
+      <c r="N25" t="n">
         <v>169.8793</v>
       </c>
-      <c r="O25">
+      <c r="O25" t="n">
         <v>185.3425</v>
       </c>
-      <c r="P25">
+      <c r="P25" t="n">
         <v>186.0519</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" t="n">
         <v>208.3234</v>
       </c>
-      <c r="R25">
+      <c r="R25" t="n">
         <v>204.82</v>
       </c>
-      <c r="S25">
+      <c r="S25" t="n">
         <v>266.8655</v>
       </c>
-      <c r="T25">
+      <c r="T25" t="n">
         <v>258.2621</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26">
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>500.8827</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>658.0554</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>800.3603000000001</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>880.8167999999999</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>1106.8166</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>1339.5728</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="n">
         <v>1482.0803</v>
       </c>
-      <c r="I26">
+      <c r="I26" t="n">
         <v>1731.2618</v>
       </c>
-      <c r="J26">
+      <c r="J26" t="n">
         <v>2082.44</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="n">
         <v>2726.8543</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>3136.4923</v>
       </c>
-      <c r="M26">
+      <c r="M26" t="n">
         <v>3332.1303</v>
       </c>
-      <c r="N26">
+      <c r="N26" t="n">
         <v>3538.4054</v>
       </c>
-      <c r="O26">
+      <c r="O26" t="n">
         <v>3773.3831</v>
       </c>
-      <c r="P26">
+      <c r="P26" t="n">
         <v>3857.3887</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" t="n">
         <v>4257.6972</v>
       </c>
-      <c r="R26">
+      <c r="R26" t="n">
         <v>4012.439</v>
       </c>
-      <c r="S26">
+      <c r="S26" t="n">
         <v>4112.7833</v>
       </c>
-      <c r="T26">
+      <c r="T26" t="n">
         <v>3914.1809</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="A27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27">
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>77.3736</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>95.872</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>110.0366</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>125.9614</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>163.6303</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>221.2284</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="n">
         <v>272.2764</v>
       </c>
-      <c r="I27">
+      <c r="I27" t="n">
         <v>315.1233</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="n">
         <v>343.4745</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>375.0529</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>410.7238</v>
       </c>
-      <c r="M27">
+      <c r="M27" t="n">
         <v>460.8886</v>
       </c>
-      <c r="N27">
+      <c r="N27" t="n">
         <v>519.6778</v>
       </c>
-      <c r="O27">
+      <c r="O27" t="n">
         <v>569.1283</v>
       </c>
-      <c r="P27">
+      <c r="P27" t="n">
         <v>632.1928</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" t="n">
         <v>681.3579999999999</v>
       </c>
-      <c r="R27">
+      <c r="R27" t="n">
         <v>692.1599</v>
       </c>
-      <c r="S27">
+      <c r="S27" t="n">
         <v>737.8942</v>
       </c>
-      <c r="T27">
+      <c r="T27" t="n">
         <v>746.0773</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="A28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28">
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>115.6184</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>146.5641</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>168.8559</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>195.2612</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>247.8206</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>320.0356</v>
       </c>
-      <c r="H28">
+      <c r="H28" t="n">
         <v>382.0151</v>
       </c>
-      <c r="I28">
+      <c r="I28" t="n">
         <v>453.969</v>
       </c>
-      <c r="J28">
+      <c r="J28" t="n">
         <v>510.8707</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>560.4635</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>598.9113</v>
       </c>
-      <c r="M28">
+      <c r="M28" t="n">
         <v>634.1633</v>
       </c>
-      <c r="N28">
+      <c r="N28" t="n">
         <v>680.3797</v>
       </c>
-      <c r="O28">
+      <c r="O28" t="n">
         <v>668.076</v>
       </c>
-      <c r="P28">
+      <c r="P28" t="n">
         <v>675.6083</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" t="n">
         <v>749.847</v>
       </c>
-      <c r="R28">
+      <c r="R28" t="n">
         <v>698.5234</v>
       </c>
-      <c r="S28">
+      <c r="S28" t="n">
         <v>754.0813000000001</v>
       </c>
-      <c r="T28">
+      <c r="T28" t="n">
         <v>750.4953</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
-      <c r="A29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29">
+      <c r="U28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>西宁</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>14.1598</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>18.4123</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>23.4468</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>28.1495</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>34.5219</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>45.2473</v>
       </c>
-      <c r="H29">
+      <c r="H29" t="n">
         <v>54.767</v>
       </c>
-      <c r="I29">
+      <c r="I29" t="n">
         <v>67.1138</v>
       </c>
-      <c r="J29">
+      <c r="J29" t="n">
         <v>83.88209999999999</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="n">
         <v>94.7861</v>
       </c>
-      <c r="L29">
+      <c r="L29" t="n">
         <v>75.2163</v>
       </c>
-      <c r="M29">
+      <c r="M29" t="n">
         <v>79.1623</v>
       </c>
-      <c r="N29">
+      <c r="N29" t="n">
         <v>92.9435</v>
       </c>
-      <c r="O29">
+      <c r="O29" t="n">
         <v>101.7897</v>
       </c>
-      <c r="P29">
+      <c r="P29" t="n">
         <v>133.5075</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" t="n">
         <v>153.8668</v>
       </c>
-      <c r="R29">
+      <c r="R29" t="n">
         <v>131.7174</v>
       </c>
-      <c r="S29">
+      <c r="S29" t="n">
         <v>144.0917</v>
       </c>
-      <c r="T29">
+      <c r="T29" t="n">
         <v>134.4576</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30">
+      <c r="U29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>85.8854</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>112.9189</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>145.6087</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>181.3992</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>241.8567</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>318.5486</v>
       </c>
-      <c r="H30">
+      <c r="H30" t="n">
         <v>396.9597</v>
       </c>
-      <c r="I30">
+      <c r="I30" t="n">
         <v>501.9751</v>
       </c>
-      <c r="J30">
+      <c r="J30" t="n">
         <v>583.7888</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="n">
         <v>650.9853000000001</v>
       </c>
-      <c r="L30">
+      <c r="L30" t="n">
         <v>641.0655</v>
       </c>
-      <c r="M30">
+      <c r="M30" t="n">
         <v>654.4997</v>
       </c>
-      <c r="N30">
+      <c r="N30" t="n">
         <v>684.7035</v>
       </c>
-      <c r="O30">
+      <c r="O30" t="n">
         <v>702.5624</v>
       </c>
-      <c r="P30">
+      <c r="P30" t="n">
         <v>724.139</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" t="n">
         <v>855.999</v>
       </c>
-      <c r="R30">
+      <c r="R30" t="n">
         <v>834.0794</v>
       </c>
-      <c r="S30">
+      <c r="S30" t="n">
         <v>951.9208</v>
       </c>
-      <c r="T30">
+      <c r="T30" t="n">
         <v>1002.3586</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
-      <c r="A31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31">
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>61.5798</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>75.91540000000001</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>88.989</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>105.3636</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>136.3034</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="n">
         <v>187.094</v>
       </c>
-      <c r="H31">
+      <c r="H31" t="n">
         <v>241.192</v>
       </c>
-      <c r="I31">
+      <c r="I31" t="n">
         <v>277.2077</v>
       </c>
-      <c r="J31">
+      <c r="J31" t="n">
         <v>331.5962</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="n">
         <v>374.1</v>
       </c>
-      <c r="L31">
+      <c r="L31" t="n">
         <v>366.3181</v>
       </c>
-      <c r="M31">
+      <c r="M31" t="n">
         <v>377.8473</v>
       </c>
-      <c r="N31">
+      <c r="N31" t="n">
         <v>411.3402</v>
       </c>
-      <c r="O31">
+      <c r="O31" t="n">
         <v>417.261</v>
       </c>
-      <c r="P31">
+      <c r="P31" t="n">
         <v>398.1279</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" t="n">
         <v>403.7174</v>
       </c>
-      <c r="R31">
+      <c r="R31" t="n">
         <v>402.1565</v>
       </c>
-      <c r="S31">
+      <c r="S31" t="n">
         <v>446.2045</v>
       </c>
-      <c r="T31">
+      <c r="T31" t="n">
         <v>434.0855</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
-      <c r="A32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32">
+      <c r="U31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
         <v>176.0266</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>219.5183</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>260.3899</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>301.9248</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>386.804</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>502.3175</v>
       </c>
-      <c r="H32">
+      <c r="H32" t="n">
         <v>606.6488000000001</v>
       </c>
-      <c r="I32">
+      <c r="I32" t="n">
         <v>723.6091</v>
       </c>
-      <c r="J32">
+      <c r="J32" t="n">
         <v>833.8761</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="n">
         <v>942.8968</v>
       </c>
-      <c r="L32">
+      <c r="L32" t="n">
         <v>1011.1833</v>
       </c>
-      <c r="M32">
+      <c r="M32" t="n">
         <v>1056.6713</v>
       </c>
-      <c r="N32">
+      <c r="N32" t="n">
         <v>1152.0568</v>
       </c>
-      <c r="O32">
+      <c r="O32" t="n">
         <v>1222.5346</v>
       </c>
-      <c r="P32">
+      <c r="P32" t="n">
         <v>1259.2106</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" t="n">
         <v>1223.628</v>
       </c>
-      <c r="R32">
+      <c r="R32" t="n">
         <v>1130.7855</v>
       </c>
-      <c r="S32">
+      <c r="S32" t="n">
         <v>1165.8481</v>
       </c>
-      <c r="T32">
+      <c r="T32" t="n">
         <v>1155.038</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
-      <c r="A33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33">
+      <c r="U32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>317.7165</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>442.7</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>577.5738</v>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>655.1701</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>952.0744999999999</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="n">
         <v>1488.33</v>
       </c>
-      <c r="H33">
+      <c r="H33" t="n">
         <v>1703.4885</v>
       </c>
-      <c r="I33">
+      <c r="I33" t="n">
         <v>1693.2438</v>
       </c>
-      <c r="J33">
+      <c r="J33" t="n">
         <v>1922.0159</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="n">
         <v>2154.83</v>
       </c>
-      <c r="L33">
+      <c r="L33" t="n">
         <v>2227.91</v>
       </c>
-      <c r="M33">
+      <c r="M33" t="n">
         <v>2252.3788</v>
       </c>
-      <c r="N33">
+      <c r="N33" t="n">
         <v>2265.5421</v>
       </c>
-      <c r="O33">
+      <c r="O33" t="n">
         <v>2134.9326</v>
       </c>
-      <c r="P33">
+      <c r="P33" t="n">
         <v>2094.8541</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" t="n">
         <v>2285.4533</v>
       </c>
-      <c r="R33">
+      <c r="R33" t="n">
         <v>2103.4234</v>
       </c>
-      <c r="S33">
+      <c r="S33" t="n">
         <v>2440.77</v>
       </c>
-      <c r="T33">
+      <c r="T33" t="n">
         <v>2595.5465</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
-      <c r="A34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34">
+      <c r="U33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>23.612</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>27.6384</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>35.811</v>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>44.0581</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>64.0368</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="n">
         <v>96.6202</v>
       </c>
-      <c r="H34">
+      <c r="H34" t="n">
         <v>113.132</v>
       </c>
-      <c r="I34">
+      <c r="I34" t="n">
         <v>134.5999</v>
       </c>
-      <c r="J34">
+      <c r="J34" t="n">
         <v>153.5998</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="n">
         <v>171.2788</v>
       </c>
-      <c r="L34">
+      <c r="L34" t="n">
         <v>173.196</v>
       </c>
-      <c r="M34">
+      <c r="M34" t="n">
         <v>177.4561</v>
       </c>
-      <c r="N34">
+      <c r="N34" t="n">
         <v>173.2544</v>
       </c>
-      <c r="O34">
+      <c r="O34" t="n">
         <v>154.7084</v>
       </c>
-      <c r="P34">
+      <c r="P34" t="n">
         <v>157.2599</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" t="n">
         <v>171.1877</v>
       </c>
-      <c r="R34">
+      <c r="R34" t="n">
         <v>168.8603</v>
       </c>
-      <c r="S34">
+      <c r="S34" t="n">
         <v>197.7591</v>
       </c>
-      <c r="T34">
+      <c r="T34" t="n">
         <v>208.4427</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35">
+      <c r="U34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
         <v>71.5908</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>93.29510000000001</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>119.0315</v>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>142.6506</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>180.8461</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>288.6312</v>
       </c>
-      <c r="H35">
+      <c r="H35" t="n">
         <v>340.8021</v>
       </c>
-      <c r="I35">
+      <c r="I35" t="n">
         <v>381.8178</v>
       </c>
-      <c r="J35">
+      <c r="J35" t="n">
         <v>397.3249</v>
       </c>
-      <c r="K35">
+      <c r="K35" t="n">
         <v>388.2213</v>
       </c>
-      <c r="L35">
+      <c r="L35" t="n">
         <v>415.4853</v>
       </c>
-      <c r="M35">
+      <c r="M35" t="n">
         <v>450.0818</v>
       </c>
-      <c r="N35">
+      <c r="N35" t="n">
         <v>478.0141</v>
       </c>
-      <c r="O35">
+      <c r="O35" t="n">
         <v>420.0168</v>
       </c>
-      <c r="P35">
+      <c r="P35" t="n">
         <v>440.4297</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" t="n">
         <v>617.0888</v>
       </c>
-      <c r="R35">
+      <c r="R35" t="n">
         <v>459.6907</v>
       </c>
-      <c r="S35">
+      <c r="S35" t="n">
         <v>576.5154</v>
       </c>
-      <c r="T35">
+      <c r="T35" t="n">
         <v>427.4842</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36">
+      <c r="U35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
         <v>132.8345</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>174.5761</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>205.5699</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>246.33</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>314.2836</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>425.7827</v>
       </c>
-      <c r="H36">
+      <c r="H36" t="n">
         <v>490.6482</v>
       </c>
-      <c r="I36">
+      <c r="I36" t="n">
         <v>536.6331</v>
       </c>
-      <c r="J36">
+      <c r="J36" t="n">
         <v>632.7992</v>
       </c>
-      <c r="K36">
+      <c r="K36" t="n">
         <v>718.9468000000001</v>
       </c>
-      <c r="L36">
+      <c r="L36" t="n">
         <v>743.6953999999999</v>
       </c>
-      <c r="M36">
+      <c r="M36" t="n">
         <v>800.3456</v>
       </c>
-      <c r="N36">
+      <c r="N36" t="n">
         <v>879.7071999999999</v>
       </c>
-      <c r="O36">
+      <c r="O36" t="n">
         <v>950.229</v>
       </c>
-      <c r="P36">
+      <c r="P36" t="n">
         <v>1100.091</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" t="n">
         <v>1188.3057</v>
       </c>
-      <c r="R36">
+      <c r="R36" t="n">
         <v>1202.0004</v>
       </c>
-      <c r="S36">
+      <c r="S36" t="n">
         <v>1227.0734</v>
       </c>
-      <c r="T36">
+      <c r="T36" t="n">
         <v>1264.5415</v>
       </c>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37">
+      <c r="U36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>225.9904</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>292.8037</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>342.4359</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>377.0086</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>452.6138</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="n">
         <v>566.14</v>
       </c>
-      <c r="H37">
+      <c r="H37" t="n">
         <v>670.182</v>
       </c>
-      <c r="I37">
+      <c r="I37" t="n">
         <v>788.9313</v>
       </c>
-      <c r="J37">
+      <c r="J37" t="n">
         <v>895.245</v>
       </c>
-      <c r="K37">
+      <c r="K37" t="n">
         <v>1006.322</v>
       </c>
-      <c r="L37">
+      <c r="L37" t="n">
         <v>1100.0303</v>
       </c>
-      <c r="M37">
+      <c r="M37" t="n">
         <v>1157.2389</v>
       </c>
-      <c r="N37">
+      <c r="N37" t="n">
         <v>1231.9138</v>
       </c>
-      <c r="O37">
+      <c r="O37" t="n">
         <v>1241.7359</v>
       </c>
-      <c r="P37">
+      <c r="P37" t="n">
         <v>1253.8548</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" t="n">
         <v>1368.2971</v>
       </c>
-      <c r="R37">
+      <c r="R37" t="n">
         <v>1273.3096</v>
       </c>
-      <c r="S37">
+      <c r="S37" t="n">
         <v>1337.8595</v>
       </c>
-      <c r="T37">
+      <c r="T37" t="n">
         <v>1339.2553</v>
       </c>
+      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data_raw/city_income.xlsx
+++ b/data_raw/city_income.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,11 +529,6 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -598,7 +593,6 @@
       <c r="T2" t="n">
         <v>8374.166499999999</v>
       </c>
-      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -663,7 +657,6 @@
       <c r="T3" t="n">
         <v>371.3048</v>
       </c>
-      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -728,7 +721,6 @@
       <c r="T4" t="n">
         <v>251.9062</v>
       </c>
-      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -793,7 +785,6 @@
       <c r="T5" t="n">
         <v>6372.6778</v>
       </c>
-      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -858,7 +849,6 @@
       <c r="T6" t="n">
         <v>1596.0247</v>
       </c>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -923,7 +913,6 @@
       <c r="T7" t="n">
         <v>381.1575</v>
       </c>
-      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -988,7 +977,6 @@
       <c r="T8" t="n">
         <v>526.2059</v>
       </c>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1053,7 +1041,6 @@
       <c r="T9" t="n">
         <v>933.3486</v>
       </c>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1118,7 +1105,6 @@
       <c r="T10" t="n">
         <v>955.0095</v>
       </c>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1183,7 +1169,6 @@
       <c r="T11" t="n">
         <v>255.1216</v>
       </c>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1246,7 +1231,6 @@
       <c r="T12" t="n">
         <v>337.8436</v>
       </c>
-      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1311,7 +1295,6 @@
       <c r="T13" t="n">
         <v>774.7741</v>
       </c>
-      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1376,7 +1359,6 @@
       <c r="T14" t="n">
         <v>2134.1963</v>
       </c>
-      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1441,7 +1423,6 @@
       <c r="T15" t="n">
         <v>440.2649</v>
       </c>
-      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1506,7 +1487,6 @@
       <c r="T16" t="n">
         <v>1790.4654</v>
       </c>
-      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1571,7 +1551,6 @@
       <c r="T17" t="n">
         <v>1954.7351</v>
       </c>
-      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1636,7 +1615,6 @@
       <c r="T18" t="n">
         <v>1949.4956</v>
       </c>
-      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1701,7 +1679,6 @@
       <c r="T19" t="n">
         <v>120.6387</v>
       </c>
-      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1764,7 +1741,6 @@
       <c r="T20" t="n">
         <v>547.2211</v>
       </c>
-      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1829,7 +1805,6 @@
       <c r="T21" t="n">
         <v>2640.3344</v>
       </c>
-      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1894,7 +1869,6 @@
       <c r="T22" t="n">
         <v>1667.3101</v>
       </c>
-      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1959,7 +1933,6 @@
       <c r="T23" t="n">
         <v>825.5809</v>
       </c>
-      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2024,7 +1997,6 @@
       <c r="T24" t="n">
         <v>1083.0473</v>
       </c>
-      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2089,7 +2061,6 @@
       <c r="T25" t="n">
         <v>258.2621</v>
       </c>
-      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2154,7 +2125,6 @@
       <c r="T26" t="n">
         <v>3914.1809</v>
       </c>
-      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2219,7 +2189,6 @@
       <c r="T27" t="n">
         <v>746.0773</v>
       </c>
-      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2284,7 +2253,6 @@
       <c r="T28" t="n">
         <v>750.4953</v>
       </c>
-      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2349,7 +2317,6 @@
       <c r="T29" t="n">
         <v>134.4576</v>
       </c>
-      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2414,7 +2381,6 @@
       <c r="T30" t="n">
         <v>1002.3586</v>
       </c>
-      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2479,7 +2445,6 @@
       <c r="T31" t="n">
         <v>434.0855</v>
       </c>
-      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2544,7 +2509,6 @@
       <c r="T32" t="n">
         <v>1155.038</v>
       </c>
-      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -2609,7 +2573,6 @@
       <c r="T33" t="n">
         <v>2595.5465</v>
       </c>
-      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -2674,7 +2637,6 @@
       <c r="T34" t="n">
         <v>208.4427</v>
       </c>
-      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -2739,7 +2701,6 @@
       <c r="T35" t="n">
         <v>427.4842</v>
       </c>
-      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -2804,7 +2765,6 @@
       <c r="T36" t="n">
         <v>1264.5415</v>
       </c>
-      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -2869,7 +2829,6 @@
       <c r="T37" t="n">
         <v>1339.2553</v>
       </c>
-      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
